--- a/docs/research/provinces/SportsHub-Quebec.xlsx
+++ b/docs/research/provinces/SportsHub-Quebec.xlsx
@@ -11,12 +11,14 @@
     <sheet name="Leagues" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Club-League Map" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Contacts" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Club Sizes" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Clubs'!$A$1:$P$177</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Leagues'!$A$1:$L$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Club-League Map'!$A$1:$E$81</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Contacts'!$A$1:$F$177</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Club Sizes'!$A$1:$C$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -557,10 +559,6 @@
           <t>Alma</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Simon Leblanc, Cyrille Poitevineau-Millin, Samuel Guay — co-founders</t>
@@ -571,13 +569,11 @@
           <t>Turnkey support structure (OBNL) for school and civil youth basketball teams in MRC Lac-Saint-Jean-Est; plans to extend around Lac-Saint-Jean</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
           <t>community nonprofit (OBNL)</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>reported</t>
@@ -620,7 +616,6 @@
           <t>19, avenue Marquette, Baie-Comeau, QC G4Z 1K5</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>abmbc01@gmail.com</t>
@@ -631,19 +626,16 @@
           <t>https://www.facebook.com/profile.php?id=100076065697206</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>Minor basketball (youth)</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>primary</t>
@@ -681,23 +673,16 @@
           <t>Baie-Comeau</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>(418) 589-5774</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
           <t>unité régionale de loisir et sport</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>primary</t>
@@ -708,7 +693,6 @@
           <t>Basketball Québec regional registry PDFs (mined 2026-07-18)</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -761,13 +745,11 @@
           <t>Mini-Pionniers community mini-basket plus Pionniers teams (benjamin féminin D4 team won 2024 Tournoi maskoutain)</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
           <t>school-affiliated community program</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>primary</t>
@@ -805,7 +787,6 @@
           <t>Blainville</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>514-730-1466</t>
@@ -831,13 +812,11 @@
           <t>Sport-études basketball program</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>primary</t>
@@ -848,7 +827,6 @@
           <t>https://www.basketball.qc.ca/fr/page/reseau_basketball_quebec/laurentides.html</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -953,7 +931,6 @@
           <t>Boucherville</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>450-641-0693</t>
@@ -979,13 +956,11 @@
           <t>Introduction to basketball ages 6-12 (petit basket to mini), boys and girls; fun-first approach</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>verified</t>
@@ -996,7 +971,6 @@
           <t>https://basketballboucherville.ca/</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1019,7 +993,6 @@
           <t>Brossard</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>514-799-8130</t>
@@ -1097,7 +1070,6 @@
           <t>Brossard</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>514-312-0348</t>
@@ -1175,7 +1147,6 @@
           <t>Brossard</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>438-886-6677</t>
@@ -1186,7 +1157,6 @@
           <t>jackpetricich@gmail.com</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Jacob Petricich — contact/lead</t>
@@ -1197,13 +1167,11 @@
           <t>Basketball training program (Basketball Québec affiliate)</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -1241,7 +1209,6 @@
           <t>Candiac / Delson / La Prairie</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>514-946-3404</t>
@@ -1252,7 +1219,6 @@
           <t>cpierre30@gmail.com</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Christopher Pierre — contact/lead</t>
@@ -1263,13 +1229,11 @@
           <t>Youth basketball academy (Roussillon area)</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>primary</t>
@@ -1307,7 +1271,6 @@
           <t>Candiac / Delson / La Prairie</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>514-946-3404</t>
@@ -1333,13 +1296,11 @@
           <t>Community youth basketball for Roussillon MRC towns</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>primary</t>
@@ -1350,7 +1311,6 @@
           <t>https://www.basketball.qc.ca/fr/page/reseau_basketball_quebec/rive-sud.html</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1403,13 +1363,11 @@
           <t>Competitive team grades 5-6 (two practices/week Sept-Mar + matches vs regional teams); Camp estival MSH summer camp</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
           <t>community program / small private organization (classification not published)</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>primary</t>
@@ -1420,7 +1378,6 @@
           <t>https://swsdbasketball.com/cardinaux</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1443,14 +1400,11 @@
           <t>Centre-du-Québec</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>(819) 864-0792</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Olivier Audet</t>
@@ -1471,7 +1425,6 @@
           <t>fédération sport-étudiant (RSEQ)</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
           <t>primary</t>
@@ -1482,7 +1435,6 @@
           <t>Basketball Québec regional registry PDFs (mined 2026-07-18)</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1505,23 +1457,16 @@
           <t>Chapais</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>(418) 745-3968</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
           <t>commission de loisir et sport</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
           <t>primary</t>
@@ -1532,7 +1477,6 @@
           <t>Basketball Québec regional registry PDFs (mined 2026-07-18)</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1555,7 +1499,6 @@
           <t>Châteauguay</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>438-888-9657</t>
@@ -1633,7 +1576,6 @@
           <t>Châteauguay</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>450-507-1696</t>
@@ -1659,13 +1601,11 @@
           <t>Mini to ouvert, boys (PSO); skills training academy</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>primary</t>
@@ -1676,7 +1616,6 @@
           <t>https://www.basketball.qc.ca/fr/page/reseau_basketball_quebec/rive-sud.html</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1699,7 +1638,6 @@
           <t>Côte Saint-Luc</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>514-983-8521</t>
@@ -1735,7 +1673,6 @@
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
           <t>verified</t>
@@ -1746,7 +1683,6 @@
           <t>https://cslwarriors.ca/</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1769,13 +1705,11 @@
           <t>Dollard-des-Ormeaux</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>514-898-2637</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>https://champsmtlbasketball.com/</t>
@@ -1791,7 +1725,6 @@
           <t>800+ participants/year: school programs, summer camps, advanced training 14+, weekly training; mini to juvénile boys and girls</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
           <t>private academy</t>
@@ -1812,7 +1745,6 @@
           <t>https://champsmtlbasketball.com/programs/</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1835,7 +1767,6 @@
           <t>Dollard-des-Ormeaux</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>514-791-0738</t>
@@ -1861,13 +1792,11 @@
           <t>Community basketball for Filipino community, West Island</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
           <t>multi-sport org</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>primary</t>
@@ -1878,7 +1807,6 @@
           <t>https://www.basketball.qc.ca/fr/page/reseau_basketball_quebec/montreal.html</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1931,7 +1859,6 @@
           <t>Mini-basket ages 6-12, 10-week fall session (Saturdays), $75; part of broader multi-sport community programming</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
           <t>multi-sport community org</t>
@@ -1952,7 +1879,6 @@
           <t>https://www.ccrsjb.qc.ca/activites/mini-basket</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1975,7 +1901,6 @@
           <t>Drummondville</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>819-469-1601</t>
@@ -2083,7 +2008,6 @@
           <t>Elite summer basketball camps for youth (3rd edition Aug 9-14, 2026 at École secondaire Marie-Rivier; boarding + meals option; elite groups scrimmage college teams)</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
           <t>private academy / camp company</t>
@@ -2131,23 +2055,16 @@
           <t>Drummondville</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>(819) 478-1483</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
           <t>unité régionale de loisir et sport</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
           <t>primary</t>
@@ -2158,7 +2075,6 @@
           <t>Basketball Québec regional registry PDFs (mined 2026-07-18)</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2181,7 +2097,6 @@
           <t>Fort-Coulonge</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>514-621-5738</t>
@@ -2207,13 +2122,11 @@
           <t>Overcomers Development, Overcomers Prep, Overcomers Next — skill development, performance fitness, mentorship</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
           <t>primary</t>
@@ -2251,7 +2164,6 @@
           <t>Gatineau</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>819-918-9885</t>
@@ -2277,7 +2189,6 @@
           <t>Junior development program (young beginners to experienced players); adult league; talent identification and training</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
           <t>private academy (mission-driven; incorporation status not published)</t>
@@ -2325,7 +2236,6 @@
           <t>Gatineau</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>438-924-2522</t>
@@ -2336,20 +2246,16 @@
           <t>ch.david@live.ca</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>David Chamoun — contact per Basketball Québec regional registry</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
           <t>school-affiliated program (uncertain)</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -2469,7 +2375,6 @@
           <t>Gatineau</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>819-639-7542</t>
@@ -2480,20 +2385,16 @@
           <t>basketball.secteurest@gmail.com</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>Joel Belleau — Basketball Québec registry contact</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
           <t>primary</t>
@@ -2643,7 +2544,6 @@
           <t>Community mini-basket (novice &amp; mini, boys and girls) feeding from ~15 primary schools of the Draveurs school-board sector; coached by Nicolas-Gatineau students; elite school program secondary D1-D3</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
           <t>school-affiliated community mini-basket program</t>
@@ -2691,10 +2591,6 @@
           <t>Gatineau</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>Jean Duchesne</t>
@@ -2705,13 +2601,11 @@
           <t>novice et mini *fém&amp;masc</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
           <t>Basketball Club</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
           <t>primary</t>
@@ -2722,7 +2616,6 @@
           <t>Basketball Québec regional registry PDFs (mined 2026-07-18)</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2745,7 +2638,6 @@
           <t>Gatineau</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>819-208-7860</t>
@@ -2771,13 +2663,11 @@
           <t>Mini-basket for novice/mini (elementary grades), M/F; ~300 children in 15+ elementary schools coached by ~20 Nicolas-Gatineau student-coaches; teams play 5 tournaments per year</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
           <t>school-affiliated community program (École polyvalente Nicolas-Gatineau)</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
           <t>primary</t>
@@ -2815,14 +2705,11 @@
           <t>Gatineau</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>(819) 643-6663</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>Hélène Boucher</t>
@@ -2833,13 +2720,11 @@
           <t>Sport Étudiant</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
           <t>Student Sport Network</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
           <t>primary</t>
@@ -2850,7 +2735,6 @@
           <t>Basketball Québec regional registry PDFs (mined 2026-07-18)</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2873,7 +2757,6 @@
           <t>Gatineau (secteur Est — Buckingham/Masson-Angers)</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>819-639-7542</t>
@@ -2884,20 +2767,16 @@
           <t>basketball.secteurest@gmail.com</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>Joel Belleau — contact per Basketball Québec regional registry</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
           <t>primary</t>
@@ -2965,7 +2844,6 @@
           <t>Youth basketball courses (mini-basket page; instructor from Cégep de Granby team; next registrations fall 2026; boys 10-12 two levels) plus women's 16+ open-play basketball</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
           <t>multi-sport org</t>
@@ -3033,13 +2911,11 @@
           <t>https://granbymultisports.ca/activite/mini-basket/</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>Youth basketball courses adapted to skill level ('Basketball Indigo', next registrations fall 2026); also adult drop-in basketball ($10/session) at École J.-H.-Leclerc; carte-loisirs discounts for under-17s</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
           <t>multi-sport org (community nonprofit)</t>
@@ -3117,7 +2993,6 @@
           <t>Youth basketball ages 8-12 (mixed 8-9; boys 10-12 beginner/intermediate and advanced; girls grades 5-6 &amp; secondary 1-2); Saturday sessions ~$130/session; run in collaboration with the cégep's L'Indigo teams and coaches; spring/summer recruitment camps</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
           <t>institution-run community youth program (cégep)</t>
@@ -3165,14 +3040,11 @@
           <t>Jonquière</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>418-376-4281</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>Jean Ménard</t>
@@ -3183,13 +3055,11 @@
           <t>petit basket, Mini, Atome, Benjamin, Cadet, Juvénile * Masculin &amp; Féminin</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
           <t>Club</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
           <t>primary</t>
@@ -3200,7 +3070,6 @@
           <t>Basketball Québec regional registry PDFs (mined 2026-07-18)</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3223,27 +3092,21 @@
           <t>L'Épiphanie</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
           <t>1-866-588-4443</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
           <t>regional sport council</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
           <t>primary</t>
@@ -3254,7 +3117,6 @@
           <t>Basketball Québec regional registry PDFs (mined 2026-07-18)</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3277,7 +3139,6 @@
           <t>Lac-Beauport</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
           <t>418-805-3145</t>
@@ -3288,7 +3149,6 @@
           <t>melgauthier07@gmail.com</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>Mélanie Gauthier — contact (same person as EMBQ administration)</t>
@@ -3299,13 +3159,11 @@
           <t>Sport development institute; appears to be the umbrella/sport-études entity affiliated with EMBQ</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
           <t>nonprofit sport institute (EMBQ-affiliated)</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
           <t>primary</t>
@@ -3343,7 +3201,6 @@
           <t>Lac-Saint-Joseph</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>418-454-2783</t>
@@ -3354,20 +3211,16 @@
           <t>fournier_laurent@hotmail.com</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>Laurent Fournier — contact in Basketball Québec directory (role unspecified)</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
           <t>primary</t>
@@ -3405,7 +3258,6 @@
           <t>Lac-Saint-Joseph (Québec City area)</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>418-454-2783</t>
@@ -3416,20 +3268,16 @@
           <t>fournier_laurent@hotmail.com</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>Laurent Fournier (PSO-listed contact)</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
           <t>unknown (community club per PSO listing)</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -3467,14 +3315,11 @@
           <t>Laval</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
           <t>(514) 970-2232</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>David Osmann</t>
@@ -3485,13 +3330,11 @@
           <t>Benjamin et Cadet Féminin</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
           <t>Basketball Club</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
           <t>primary</t>
@@ -3502,7 +3345,6 @@
           <t>Basketball Québec regional registry PDFs (mined 2026-07-18)</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3525,14 +3367,11 @@
           <t>Laval</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>(514) 970-2232</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>David Osmann — contact (PSO registry)</t>
@@ -3543,13 +3382,11 @@
           <t>Girls benjamin and cadet</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
           <t>primary</t>
@@ -3587,7 +3424,6 @@
           <t>Laval</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>514-553-8422</t>
@@ -3638,7 +3474,6 @@
           <t>https://www.basketlaval.ca/?lang=en</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3661,14 +3496,11 @@
           <t>Laval</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>514-464-5203</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>Eric Denis</t>
@@ -3679,13 +3511,11 @@
           <t>5 à 17ans de petit basket à juvénile *fém&amp;masc</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
           <t>Basketball Club</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
           <t>primary</t>
@@ -3696,7 +3526,6 @@
           <t>Basketball Québec regional registry PDFs (mined 2026-07-18)</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3774,7 +3603,6 @@
           <t>https://millerbasketballacademy.ca/</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3827,13 +3655,11 @@
           <t>Basketball academy training (Laval)</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -3871,14 +3697,11 @@
           <t>Laval</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
           <t>(450) 664-1917</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>Martin Savoie</t>
@@ -3889,13 +3712,11 @@
           <t>Sport-étudiant</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
           <t>Sport-étudiant (Student Sport)</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
           <t>primary</t>
@@ -3906,7 +3727,6 @@
           <t>Basketball Québec regional registry PDFs (mined 2026-07-18)</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3929,10 +3749,6 @@
           <t>Limoilou</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>Martin Thibault</t>
@@ -3943,13 +3759,11 @@
           <t>Benjamin et juvénile masculin</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
           <t>School program</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
           <t>primary</t>
@@ -3960,7 +3774,6 @@
           <t>Basketball Québec regional registry PDFs (mined 2026-07-18)</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3983,7 +3796,6 @@
           <t>Longueuil</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
           <t>(514) 908-2219</t>
@@ -4034,7 +3846,6 @@
           <t>https://tornades.org/</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4057,7 +3868,6 @@
           <t>Longueuil (Saint-Hubert)</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>438-831-1045</t>
@@ -4093,7 +3903,6 @@
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
           <t>primary</t>
@@ -4104,7 +3913,6 @@
           <t>https://www.basketball.qc.ca/fr/page/reseau_basketball_quebec/rive-sud.html</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4127,13 +3935,11 @@
           <t>Lévis</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>(418) 930-7525</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
           <t>https://www.prospectball.com/</t>
@@ -4149,13 +3955,11 @@
           <t>Private 1-on-1 skills training (C$80/session), online training, élite summer camp for ages 12-17 held at CEP du Collège de Lévis</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
           <t>private academy / training service</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
           <t>verified</t>
@@ -4357,7 +4161,6 @@
           <t>Mont-Royal</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>514-264-8495</t>
@@ -4383,13 +4186,11 @@
           <t>Basketball academy training (private facility)</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
           <t>primary</t>
@@ -4400,7 +4201,6 @@
           <t>https://www.basketball.qc.ca/fr/page/reseau_basketball_quebec/montreal.html</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4423,7 +4223,6 @@
           <t>Mont-Tremblant</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>1-819-808-1462</t>
@@ -4449,13 +4248,11 @@
           <t>Youth basketball (Basketball Québec affiliate)</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
           <t>primary</t>
@@ -4493,7 +4290,6 @@
           <t>Montréal</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>514-518-1537</t>
@@ -4509,19 +4305,16 @@
           <t>https://www.alphacommunity.ca/</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
           <t>Youth basketball programming (Basketball Québec affiliated org)</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
           <t>primary</t>
@@ -4532,7 +4325,6 @@
           <t>https://www.basketball.qc.ca/fr/page/reseau_basketball_quebec/montreal.html</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4555,7 +4347,6 @@
           <t>Montréal</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>514-571-4964</t>
@@ -4581,13 +4372,11 @@
           <t>Youth basketball ('Born Again Basketball Enlightenment')</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
           <t>primary</t>
@@ -4598,7 +4387,6 @@
           <t>https://www.basketball.qc.ca/fr/page/reseau_basketball_quebec/montreal.html</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4621,7 +4409,6 @@
           <t>Montréal</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>514-402-8597</t>
@@ -4632,7 +4419,6 @@
           <t>plusmamadou305@gmail.com</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
           <t>Mamadou Fofana — contact</t>
@@ -4643,13 +4429,11 @@
           <t>Community basketball (Ivorian community)</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -4687,7 +4471,6 @@
           <t>Montréal</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>514-249-5658</t>
@@ -4713,13 +4496,11 @@
           <t>Youth basketball programs</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
           <t>primary</t>
@@ -4730,7 +4511,6 @@
           <t>https://www.basketball.qc.ca/fr/page/reseau_basketball_quebec/montreal.html</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4753,7 +4533,6 @@
           <t>Montréal</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
           <t>514-573-8414</t>
@@ -4764,7 +4543,6 @@
           <t>Panyp_24@hotmail.com</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
           <t>Pany Phetxayakhoth — contact</t>
@@ -4775,13 +4553,11 @@
           <t>Filipino community youth teams (juvy-A finals footage vs CBO)</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
           <t>primary</t>
@@ -4792,7 +4568,6 @@
           <t>https://www.basketball.qc.ca/fr/page/reseau_basketball_quebec/montreal.html</t>
         </is>
       </c>
-      <c r="P64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4815,7 +4590,6 @@
           <t>Montréal</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>438-863-1017</t>
@@ -4826,7 +4600,6 @@
           <t>leon.arabian@gmail.com</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
           <t>Leon Arabian — contact</t>
@@ -4837,13 +4610,11 @@
           <t>Armenian community multi-sport club with basketball teams</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
           <t>multi-sport org</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr">
         <is>
           <t>primary</t>
@@ -4854,7 +4625,6 @@
           <t>https://www.basketball.qc.ca/fr/page/reseau_basketball_quebec/montreal.html</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4877,7 +4647,6 @@
           <t>Montréal</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>514-923-5464</t>
@@ -4903,13 +4672,11 @@
           <t>Basketball events/tournaments organizer (Basketball Québec affiliated)</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -4947,7 +4714,6 @@
           <t>Montréal</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
           <t>514-573-7709</t>
@@ -4983,7 +4749,6 @@
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
           <t>primary</t>
@@ -4994,7 +4759,6 @@
           <t>https://www.basketball.qc.ca/fr/page/reseau_basketball_quebec/montreal.html</t>
         </is>
       </c>
-      <c r="P67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -5017,7 +4781,6 @@
           <t>Montréal</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
           <t>514-594-3128</t>
@@ -5043,13 +4806,11 @@
           <t>Winter/spring basketball program, L.A.B. and Champions programs; juvenile girls, midget/juvenile boys; mentorship focus</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
           <t>verified</t>
@@ -5060,7 +4821,6 @@
           <t>http://www.montrealunited.ca</t>
         </is>
       </c>
-      <c r="P68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -5083,7 +4843,6 @@
           <t>Montréal</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
           <t>514-586-1526</t>
@@ -5109,13 +4868,11 @@
           <t>All categories, Filipino community youth and adult</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
           <t>primary</t>
@@ -5153,7 +4910,6 @@
           <t>Montréal</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
           <t>514-606-0978</t>
@@ -5179,7 +4935,6 @@
           <t>Mini-basket 7-12 (certified phys-ed coaches), day camps 7-17, U12 development team playing tournaments, juvénile/ouvert boys</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
           <t>private academy</t>
@@ -5227,7 +4982,6 @@
           <t>Montréal</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
           <t>514-467-9933</t>
@@ -5253,13 +5007,11 @@
           <t>Youth basketball (Basketball Québec affiliated)</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr">
         <is>
           <t>primary</t>
@@ -5270,7 +5022,6 @@
           <t>https://www.basketball.qc.ca/fr/page/reseau_basketball_quebec/montreal.html</t>
         </is>
       </c>
-      <c r="P71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -5293,7 +5044,6 @@
           <t>Montréal</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
           <t>438-274-5750</t>
@@ -5329,7 +5079,6 @@
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr">
         <is>
           <t>verified</t>
@@ -5340,7 +5089,6 @@
           <t>https://uptownmontrealbasketball.org/</t>
         </is>
       </c>
-      <c r="P72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -5363,7 +5111,6 @@
           <t>Montréal (Cartierville)</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
           <t>514-942-5020</t>
@@ -5389,13 +5136,11 @@
           <t>Youth basketball (Basketball Québec affiliated)</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
           <t>primary</t>
@@ -5433,7 +5178,6 @@
           <t>Montréal (Centre-Nord)</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
           <t>514-229-2259</t>
@@ -5459,13 +5203,11 @@
           <t>Youth basketball in Montréal's Centre-Nord district</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
           <t>primary</t>
@@ -5476,7 +5218,6 @@
           <t>https://www.basketball.qc.ca/fr/page/reseau_basketball_quebec/montreal.html</t>
         </is>
       </c>
-      <c r="P74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5499,7 +5240,6 @@
           <t>Montréal (Côte Saint-Luc)</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
           <t>514-239-4954</t>
@@ -5510,7 +5250,6 @@
           <t>edtupaz@videotron.ca</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>Edgardo Tupaz — contact/organizer</t>
@@ -5521,13 +5260,11 @@
           <t>Filipino community youth ages 7-17</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr">
         <is>
           <t>primary</t>
@@ -5538,7 +5275,6 @@
           <t>https://www.basketball.qc.ca/fr/page/reseau_basketball_quebec/montreal.html</t>
         </is>
       </c>
-      <c r="P75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5591,13 +5327,11 @@
           <t>Small Ball to Master boys, Midget and Open girls — community league for Filipino community</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr">
         <is>
           <t>primary</t>
@@ -5635,7 +5369,6 @@
           <t>Montréal (LaSalle)</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
           <t>514-833-1214</t>
@@ -5686,7 +5419,6 @@
           <t>https://leadersbasketball.com/pages/novice</t>
         </is>
       </c>
-      <c r="P77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5709,14 +5441,11 @@
           <t>Montréal (LaSalle)</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
           <t>514-788-3938</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
           <t>Sébastien Babeux — contact (PSO registry)</t>
@@ -5727,13 +5456,11 @@
           <t>Benjamin-cadet-juvénile, boys and girls</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr">
         <is>
           <t>multi-sport org</t>
         </is>
       </c>
-      <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr">
         <is>
           <t>primary</t>
@@ -5771,7 +5498,6 @@
           <t>Montréal (LaSalle)</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
           <t>514-816-6232</t>
@@ -5797,13 +5523,11 @@
           <t>Benjamin to ouvert, boys and girls; leadership/mentorship programming</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr">
         <is>
           <t>primary</t>
@@ -5841,7 +5565,6 @@
           <t>Montréal (Lachine)</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
           <t>514-829-9849</t>
@@ -5852,7 +5575,6 @@
           <t>janetlawrence61@gmail.com</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
           <t>Janet Lawrence — contact (Basketball Québec); Avrom Coodin — contact (PSO PDF)</t>
@@ -5863,13 +5585,11 @@
           <t>Novice and benjamin, boys and girls</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr">
         <is>
           <t>primary</t>
@@ -5907,7 +5627,6 @@
           <t>Montréal (Montréal-Nord)</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
           <t>514-472-0223</t>
@@ -5958,7 +5677,6 @@
           <t>https://www.zeffy.com/en-US/ticketing/adhesions-de-club-de-basketball-de-montral-nord-cbmn--2025</t>
         </is>
       </c>
-      <c r="P81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -6021,7 +5739,6 @@
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr">
         <is>
           <t>verified</t>
@@ -6114,7 +5831,6 @@
           <t>http://www.brookwoodbasketball.org/</t>
         </is>
       </c>
-      <c r="P83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -6137,7 +5853,6 @@
           <t>Montréal (Plateau/Saint-Michel)</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
           <t>514-967-2675</t>
@@ -6173,7 +5888,6 @@
           <t>multi-sport org</t>
         </is>
       </c>
-      <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr">
         <is>
           <t>verified</t>
@@ -6211,7 +5925,6 @@
           <t>Montréal (Pointe-aux-Trembles, Montréal-Nord, LaSalle)</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
           <t>514-730-3840</t>
@@ -6237,13 +5950,11 @@
           <t>Free basketball training + civic engagement for under-served youth, mini to juvénile boys and girls</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr">
         <is>
           <t>verified</t>
@@ -6254,7 +5965,6 @@
           <t>https://www.lesballonsintensifs.com/les-ballons-intensifs/notre-histoire/</t>
         </is>
       </c>
-      <c r="P85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -6332,7 +6042,6 @@
           <t>https://basketballstlaurent.com/</t>
         </is>
       </c>
-      <c r="P86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -6385,13 +6094,11 @@
           <t>Novice to juvénile boys (PSO); training camps with ABEIM at Académie Dunton; east-end Montreal youth</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr">
         <is>
           <t>verified</t>
@@ -6429,7 +6136,6 @@
           <t>Montréal (Snowdon)</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
           <t>514-737-6551 #271</t>
@@ -6465,7 +6171,6 @@
           <t>multi-sport org</t>
         </is>
       </c>
-      <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr">
         <is>
           <t>verified</t>
@@ -6476,7 +6181,6 @@
           <t>https://www.basketball.qc.ca/fr/page/reseau_basketball_quebec/montreal.html</t>
         </is>
       </c>
-      <c r="P88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -6499,14 +6203,11 @@
           <t>Montréal (Villeray, St-Michel, Parc-Extension, Montréal-Nord, St-Léonard)</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
           <t>514-207-1814</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
           <t>Yasser Mohammad — contact (PSO registry)</t>
@@ -6517,13 +6218,11 @@
           <t>Atome to juvénile; Programme Sports-Emploi</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr">
         <is>
           <t>primary</t>
@@ -6561,7 +6260,6 @@
           <t>Montréal (Villeray–Saint-Michel)</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
           <t>(514) 268-9347</t>
@@ -6597,7 +6295,6 @@
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr">
         <is>
           <t>verified</t>
@@ -6635,7 +6332,6 @@
           <t>Montréal (Westmount)</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
           <t>514-266-9200</t>
@@ -6671,7 +6367,6 @@
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr">
         <is>
           <t>primary</t>
@@ -6709,14 +6404,11 @@
           <t>Montréal (downtown)</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
           <t>514-931-8731 #5032</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
           <t>Joel Tyrrell — contact (PSO registry)</t>
@@ -6737,7 +6429,6 @@
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr">
         <is>
           <t>primary</t>
@@ -6775,27 +6466,21 @@
           <t>Montréal (east end)</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
           <t>514-885-8176</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr">
         <is>
           <t>Training camps for east-Montreal youth (with DOD/Club St-Léonard at Académie Dunton)</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr">
         <is>
           <t>reported</t>
@@ -6833,13 +6518,11 @@
           <t>Montréal (east end: Montréal-Nord, St-Léonard, Anjou, Pointe-aux-Trembles)</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
           <t>514-616-5819</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr">
         <is>
           <t>https://basketball.exposureevents.com/organizations/27817/montreal-prospects-basketball</t>
@@ -6855,7 +6538,6 @@
           <t>AAU-style elite summer teams, mini to juvénile boys; for under-served east-island youth</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr">
         <is>
           <t>private academy</t>
@@ -6923,19 +6605,16 @@
           <t>https://crer.me/club-sportif/basketball-montreal-est/</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr">
         <is>
           <t>Youth basketball at Centre Récréatif Édouard-Rivet</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr">
         <is>
           <t>primary</t>
@@ -6973,14 +6652,11 @@
           <t>NDIP</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
           <t>514-774-1663</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr">
         <is>
           <t>Michel Bento</t>
@@ -6991,13 +6667,11 @@
           <t>petit basket à juvénile *féminin et masculin</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr">
         <is>
           <t>Club</t>
         </is>
       </c>
-      <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr">
         <is>
           <t>primary</t>
@@ -7008,7 +6682,6 @@
           <t>Basketball Québec regional registry PDFs (mined 2026-07-18)</t>
         </is>
       </c>
-      <c r="P96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -7031,7 +6704,6 @@
           <t>Notre-Dame-de-l'Île-Perrot (Vaudreuil-Soulanges)</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
           <t>514-774-1663</t>
@@ -7067,7 +6739,6 @@
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr">
         <is>
           <t>verified</t>
@@ -7078,7 +6749,6 @@
           <t>https://www.cavaliersbasketballouest.ca/programs</t>
         </is>
       </c>
-      <c r="P97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -7223,7 +6893,6 @@
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M99" t="inlineStr"/>
       <c r="N99" t="inlineStr">
         <is>
           <t>primary</t>
@@ -7281,13 +6950,11 @@
           <t>https://byfarsports.com/</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr">
         <is>
           <t>Mini-Basket (girls &amp; boys, grade 5 to secondary 2, Saturday mornings); 'Qulture Basket' club program (secondary 2-5, weekday evenings + Sunday); open gym; private shooting/skills training; gym/weight room</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr">
         <is>
           <t>private academy / commercial sports centre</t>
@@ -7308,7 +6975,6 @@
           <t>https://byfarsports.com/</t>
         </is>
       </c>
-      <c r="P100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -7331,7 +6997,6 @@
           <t>Québec City</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
           <t>581-992-8410</t>
@@ -7342,7 +7007,6 @@
           <t>aurelienpuech@outlook.com</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr">
         <is>
           <t>Aurélien Puech — contact in Basketball Québec directory (role unspecified)</t>
@@ -7363,7 +7027,6 @@
           <t>3x3 club</t>
         </is>
       </c>
-      <c r="M101" t="inlineStr"/>
       <c r="N101" t="inlineStr">
         <is>
           <t>primary</t>
@@ -7401,14 +7064,11 @@
           <t>Québec City</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
           <t>edembasketball@gmail.com</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr">
         <is>
           <t>Sophia Laababsi — contact in PSO registry (role unspecified)</t>
@@ -7419,13 +7079,11 @@
           <t>Categories mini to open (ouvert), girls and boys, per Basketball Québec club list</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr">
         <is>
           <t>unknown (listed as club/organization in PSO registry)</t>
         </is>
       </c>
-      <c r="M102" t="inlineStr"/>
       <c r="N102" t="inlineStr">
         <is>
           <t>primary</t>
@@ -7493,7 +7151,6 @@
           <t>Basketball school: in-school programs (e.g. École de l'Escabelle grades 4-6), summer camps (weekly August sessions), training; organizes the Challenge Hope Basketball tournament (with Rouge et Or branding)</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr">
         <is>
           <t>private academy</t>
@@ -7551,7 +7208,6 @@
           <t>418-953-7504</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr">
         <is>
           <t>https://www.mbsbasketball.ca/</t>
@@ -7567,13 +7223,11 @@
           <t>Mini MBS (grades 2-4, ~ages 7-8+), regular group training, elite program, private training, summer camps; boys and girls trained separately; teams travel to US tournaments (Boston, Maine, Massachusetts, New York) and Quebec regional tournaments</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M104" t="inlineStr"/>
       <c r="N104" t="inlineStr">
         <is>
           <t>primary</t>
@@ -7584,7 +7238,6 @@
           <t>https://www.mbsbasketball.ca/</t>
         </is>
       </c>
-      <c r="P104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -7637,13 +7290,11 @@
           <t>Training school ages 6-19: mini-basketball, group training, private lessons, elite training program, summer camps</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr">
         <is>
           <t>private academy / training school</t>
         </is>
       </c>
-      <c r="M105" t="inlineStr"/>
       <c r="N105" t="inlineStr">
         <is>
           <t>verified</t>
@@ -7681,8 +7332,6 @@
           <t>Québec City</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
           <t>onemorebasketball1@gmail.com</t>
@@ -7703,7 +7352,6 @@
           <t>Personalized small-group training (2-10 athletes/coach, 60-90 min sessions, max 15 players); coaches experienced with benjamin/cadet/juvénile ages (~ages 10-22)</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr">
         <is>
           <t>private academy (training only, no teams)</t>
@@ -7724,7 +7372,6 @@
           <t>https://onemorebasketball.com/</t>
         </is>
       </c>
-      <c r="P106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -7747,7 +7394,6 @@
           <t>Québec City</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
           <t>418-806-5899</t>
@@ -7758,7 +7404,6 @@
           <t>glecuyercourtier@gmail.com</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
           <t>Guillaume L'Ecuyer — contact in Basketball Québec directory (role unspecified)</t>
@@ -7769,13 +7414,11 @@
           <t>Runs the Tournoi des VOLTS (July 10-12, 2026 per Basketball Québec event calendar)</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr">
         <is>
           <t>club / tournament organizer (type unverified)</t>
         </is>
       </c>
-      <c r="M107" t="inlineStr"/>
       <c r="N107" t="inlineStr">
         <is>
           <t>primary</t>
@@ -7818,7 +7461,6 @@
           <t>145 Rue Bigaouette, Québec, QC G1K 4L3</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
           <t>ecolebbemonkam1@gmail.com</t>
@@ -7849,7 +7491,6 @@
           <t>private academy</t>
         </is>
       </c>
-      <c r="M108" t="inlineStr"/>
       <c r="N108" t="inlineStr">
         <is>
           <t>primary</t>
@@ -7887,7 +7528,6 @@
           <t>Québec City (Lac-Beauport)</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
           <t>418-805-3145</t>
@@ -7898,20 +7538,16 @@
           <t>melgauthier07@gmail.com</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr">
         <is>
           <t>Mélanie Gauthier (PSO-listed contact; also EMBQ administration)</t>
         </is>
       </c>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr">
         <is>
           <t>community nonprofit (apparent umbrella/affiliate of EMBQ — same contact and phone)</t>
         </is>
       </c>
-      <c r="M109" t="inlineStr"/>
       <c r="N109" t="inlineStr">
         <is>
           <t>reported</t>
@@ -8031,14 +7667,11 @@
           <t>Québec City / Chaudière-Appalaches (exact town unpublished)</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
           <t>418-805-6205</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr"/>
-      <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
           <t>Marc-André Dugas (PSO-listed contact; club initials match his name)</t>
@@ -8049,13 +7682,11 @@
           <t>Benjamin boys (per Basketball Québec club list)</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr">
         <is>
           <t>community club</t>
         </is>
       </c>
-      <c r="M111" t="inlineStr"/>
       <c r="N111" t="inlineStr">
         <is>
           <t>reported</t>
@@ -8123,7 +7754,6 @@
           <t>Recreational teams ages 3-17, competitive training, spring/summer programs, sport-études; region-wide across Lanaudière MRCs; recognized by Basketball Québec since 2004</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr">
         <is>
           <t>community nonprofit</t>
@@ -8201,7 +7831,6 @@
           <t>Recreational teams ages 3-17; competitive formations petit basket through juvénile M/F; Sport-Études program for secondary students; summer camps</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr">
         <is>
           <t>community nonprofit (incorporated 2004-04-15)</t>
@@ -8249,14 +7878,11 @@
           <t>Richelieu-Yamaska</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
           <t>(450) 463-4055 Poste 102</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr"/>
-      <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr">
         <is>
           <t>Sylvie Cornellier</t>
@@ -8267,13 +7893,11 @@
           <t>Sport Étudiant</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr">
         <is>
           <t>School sport federation</t>
         </is>
       </c>
-      <c r="M114" t="inlineStr"/>
       <c r="N114" t="inlineStr">
         <is>
           <t>primary</t>
@@ -8284,7 +7908,6 @@
           <t>Basketball Québec regional registry PDFs (mined 2026-07-18)</t>
         </is>
       </c>
-      <c r="P114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -8389,14 +8012,11 @@
           <t>Rimouski</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
           <t>418-723-1880 #2539</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr"/>
-      <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
           <t>Marc Boudreau</t>
@@ -8417,7 +8037,6 @@
           <t>fédération sport-étudiant (RSEQ)</t>
         </is>
       </c>
-      <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr">
         <is>
           <t>primary</t>
@@ -8428,7 +8047,6 @@
           <t>Basketball Québec regional registry PDFs (mined 2026-07-18)</t>
         </is>
       </c>
-      <c r="P116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -8451,7 +8069,6 @@
           <t>Rimouski</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
           <t>418-724-3439 #2014</t>
@@ -8462,7 +8079,6 @@
           <t>keven.morneau@cssphares.gouv.qc.ca</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr">
         <is>
           <t>Keven Morneau — contact in Basketball Québec directory (school board email; role unspecified)</t>
@@ -8473,13 +8089,11 @@
           <t>Select/rep basketball program</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr">
         <is>
           <t>uncertain — likely school-affiliated select program (contact is Centre de services scolaire des Phares staff)</t>
         </is>
       </c>
-      <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -8517,27 +8131,21 @@
           <t>Rock Forest</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
           <t>(819) 864-0864</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr"/>
-      <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr">
         <is>
           <t>regional sport council</t>
         </is>
       </c>
-      <c r="M118" t="inlineStr"/>
       <c r="N118" t="inlineStr">
         <is>
           <t>primary</t>
@@ -8548,7 +8156,6 @@
           <t>Basketball Québec regional registry PDFs (mined 2026-07-18)</t>
         </is>
       </c>
-      <c r="P118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -8571,14 +8178,11 @@
           <t>Rosemère</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
           <t>514-746-3478</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr"/>
-      <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr">
         <is>
           <t>David Roy — contact/lead (PSO registry)</t>
@@ -8589,13 +8193,11 @@
           <t>Girls from age 5; boys 5-11</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M119" t="inlineStr"/>
       <c r="N119" t="inlineStr">
         <is>
           <t>primary</t>
@@ -8633,14 +8235,11 @@
           <t>Rosemère</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
           <t>514-972-6765</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr"/>
-      <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr">
         <is>
           <t>Pascal Fleury</t>
@@ -8651,13 +8250,11 @@
           <t>Mini à juvénile, Masculin et féminin, Participatif et compétitif</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr">
         <is>
           <t>club</t>
         </is>
       </c>
-      <c r="M120" t="inlineStr"/>
       <c r="N120" t="inlineStr">
         <is>
           <t>primary</t>
@@ -8668,7 +8265,6 @@
           <t>Basketball Québec regional registry PDFs (mined 2026-07-18)</t>
         </is>
       </c>
-      <c r="P120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -8691,7 +8287,6 @@
           <t>Saguenay (Chicoutimi)</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
           <t>418-698-3231</t>
@@ -8727,7 +8322,6 @@
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M121" t="inlineStr"/>
       <c r="N121" t="inlineStr">
         <is>
           <t>verified</t>
@@ -8847,7 +8441,6 @@
           <t>Saguenay (Jonquière)</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
           <t>418-590-2396</t>
@@ -8873,7 +8466,6 @@
           <t>Mini-basket through juvénile (petit basket, mini, atome, benjamin, cadet, juvénile, boys &amp; girls per PSO PDF); summer mini-basket camps ages 8-12</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr">
         <is>
           <t>community nonprofit</t>
@@ -8931,7 +8523,6 @@
           <t>418-542-7536 ext. 117</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr">
         <is>
           <t>https://www.patrojonquiere.org/activites/activites-sportives/basketball/</t>
@@ -8947,7 +8538,6 @@
           <t>Recreational drop-in basketball: under-15 (Thursdays 7-8pm, free) and 16+ ($8/session), Jan-Jun</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr">
         <is>
           <t>multi-sport community org</t>
@@ -8995,7 +8585,6 @@
           <t>Saint-Barnabé-Sud (Saint-Hyacinthe area)</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
           <t>450-771-1757</t>
@@ -9021,7 +8610,6 @@
           <t>Celtics EMB youth basketball teams (operating ~7 years) drawing players from across Montérégie; competitive and development basketball, clinics, teen league</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr">
         <is>
           <t>private academy / training business (est. 2005)</t>
@@ -9042,7 +8630,6 @@
           <t>https://www.entrainementmb.com</t>
         </is>
       </c>
-      <c r="P125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -9065,7 +8652,6 @@
           <t>Saint-Barnabé-Sud (Saint-Hyacinthe area)</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
           <t>450-771-1757</t>
@@ -9091,13 +8677,11 @@
           <t>Civil youth basketball program (Celtics EMB) serving Montérégie ~7 years — mini and benjamin teams M+F; competitive &amp; development basketball; sports camps (basketball/soccer/volleyball); physical prep; co-organizes Tournoi invitation de basketball maskoutain with ESSJ Patriotes</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr">
         <is>
           <t>private academy / training business with civil club program</t>
         </is>
       </c>
-      <c r="M126" t="inlineStr"/>
       <c r="N126" t="inlineStr">
         <is>
           <t>verified</t>
@@ -9108,7 +8692,6 @@
           <t>https://entrainementmb.com</t>
         </is>
       </c>
-      <c r="P126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -9131,7 +8714,6 @@
           <t>Saint-Basile-le-Grand</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
           <t>514-431-1290</t>
@@ -9157,13 +8739,11 @@
           <t>Basketball training/facility programs (Basketball Québec affiliate)</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M127" t="inlineStr"/>
       <c r="N127" t="inlineStr">
         <is>
           <t>primary</t>
@@ -9174,7 +8754,6 @@
           <t>https://www.basketball.qc.ca/fr/page/reseau_basketball_quebec/montreal.html</t>
         </is>
       </c>
-      <c r="P127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -9197,7 +8776,6 @@
           <t>Saint-Boniface</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
           <t>819-247-0178</t>
@@ -9208,20 +8786,16 @@
           <t>matilde6@hotmail.com</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr">
         <is>
           <t>Maïka Baril — contact in Basketball Québec directory (role unspecified)</t>
         </is>
       </c>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr">
         <is>
           <t>community club</t>
         </is>
       </c>
-      <c r="M128" t="inlineStr"/>
       <c r="N128" t="inlineStr">
         <is>
           <t>primary</t>
@@ -9259,7 +8833,6 @@
           <t>Saint-Bruno-de-Montarville</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
           <t>514-984-2039</t>
@@ -9285,13 +8858,11 @@
           <t>Petit basket to juvénile, boys and girls; beginner to experienced</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M129" t="inlineStr"/>
       <c r="N129" t="inlineStr">
         <is>
           <t>verified</t>
@@ -9302,7 +8873,6 @@
           <t>https://absb.ca/association/</t>
         </is>
       </c>
-      <c r="P129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -9325,7 +8895,6 @@
           <t>Saint-Charles-Borromée (Grand Joliette)</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
           <t>514-709-5717</t>
@@ -9403,7 +8972,6 @@
           <t>Saint-Charles-Borromée (Joliette area)</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
           <t>514-709-5717</t>
@@ -9429,7 +8997,6 @@
           <t>Youth basketball (Basketball Québec affiliate)</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr">
         <is>
           <t>community nonprofit</t>
@@ -9477,7 +9044,6 @@
           <t>Saint-Eustache</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
           <t>514-261-9933</t>
@@ -9488,7 +9054,6 @@
           <t>enacheadrian2000@yahoo.ca</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr">
         <is>
           <t>Adrian Enache — contact/lead</t>
@@ -9499,13 +9064,11 @@
           <t>Competitive youth basketball (Basketball Québec affiliate)</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
       <c r="L132" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M132" t="inlineStr"/>
       <c r="N132" t="inlineStr">
         <is>
           <t>primary</t>
@@ -9516,7 +9079,6 @@
           <t>https://www.basketball.qc.ca/fr/page/reseau_basketball_quebec/laurentides.html</t>
         </is>
       </c>
-      <c r="P132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -9539,7 +9101,6 @@
           <t>Saint-Eustache</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
           <t>514-572-1939</t>
@@ -9565,13 +9126,11 @@
           <t>Community basketball club (Basketball Québec affiliate, Laval region listing)</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M133" t="inlineStr"/>
       <c r="N133" t="inlineStr">
         <is>
           <t>primary</t>
@@ -9582,7 +9141,6 @@
           <t>https://www.basketball.qc.ca/fr/page/reseau_basketball_quebec/laval.html</t>
         </is>
       </c>
-      <c r="P133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -9687,23 +9245,16 @@
           <t>Saint-Hyacinthe</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
           <t>(450) 773-9802</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr"/>
-      <c r="H135" t="inlineStr"/>
-      <c r="I135" t="inlineStr"/>
-      <c r="J135" t="inlineStr"/>
-      <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr">
         <is>
           <t>Regional sport/leisure body</t>
         </is>
       </c>
-      <c r="M135" t="inlineStr"/>
       <c r="N135" t="inlineStr">
         <is>
           <t>primary</t>
@@ -9714,7 +9265,6 @@
           <t>Basketball Québec regional registry PDFs (mined 2026-07-18)</t>
         </is>
       </c>
-      <c r="P135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -9737,14 +9287,11 @@
           <t>Saint-Hyacinthe</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
           <t>514-885-4347</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr"/>
-      <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr">
         <is>
           <t>Patrick Kervin</t>
@@ -9755,13 +9302,11 @@
           <t>Novice, mini et benjamin *féminin et masculin</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr">
         <is>
           <t>Club</t>
         </is>
       </c>
-      <c r="M136" t="inlineStr"/>
       <c r="N136" t="inlineStr">
         <is>
           <t>primary</t>
@@ -9772,7 +9317,6 @@
           <t>Basketball Québec regional registry PDFs (mined 2026-07-18)</t>
         </is>
       </c>
-      <c r="P136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -9825,7 +9369,6 @@
           <t>House leagues ('Ligues Locales') novice &amp; mini, fall (Sep-Dec) + winter (Jan-Mar) sessions; spring development clinics (May-Jun); outdoor summer league (novice-benjamin, Jun-Jul); competitive 'Riverains' teams novice through juvénile M/F; July morning training; concentration sport</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr">
         <is>
           <t>community nonprofit</t>
@@ -9955,7 +9498,6 @@
           <t>Saint-Jérôme</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
           <t>514-994-3715</t>
@@ -9981,13 +9523,11 @@
           <t>Basketball training (Basketball Québec affiliate; listed under Montréal region with St-Jérôme city)</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M139" t="inlineStr"/>
       <c r="N139" t="inlineStr">
         <is>
           <t>primary</t>
@@ -9998,7 +9538,6 @@
           <t>https://www.basketball.qc.ca/fr/page/reseau_basketball_quebec/montreal.html</t>
         </is>
       </c>
-      <c r="P139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -10021,7 +9560,6 @@
           <t>Saint-Jérôme (based Prévost)</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
           <t>514-458-2359</t>
@@ -10047,13 +9585,11 @@
           <t>Nonprofit focused on girls/women's basketball; student-athlete global development</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M140" t="inlineStr"/>
       <c r="N140" t="inlineStr">
         <is>
           <t>verified</t>
@@ -10064,7 +9600,6 @@
           <t>https://basketballstjerome.ca/</t>
         </is>
       </c>
-      <c r="P140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -10087,7 +9622,6 @@
           <t>Saint-Lambert / Saint-Bruno-de-Montarville</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
           <t>514-919-3543</t>
@@ -10113,13 +9647,11 @@
           <t>Girls summer program (April-August)</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M141" t="inlineStr"/>
       <c r="N141" t="inlineStr">
         <is>
           <t>primary</t>
@@ -10157,7 +9689,6 @@
           <t>Saint-Lazare</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
           <t>514-917-9879</t>
@@ -10168,7 +9699,6 @@
           <t>stlazarelions@gmail.com</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr"/>
       <c r="I142" t="inlineStr">
         <is>
           <t>Sophie Plante — contact/lead</t>
@@ -10179,13 +9709,11 @@
           <t>Youth basketball (Basketball Québec affiliate)</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M142" t="inlineStr"/>
       <c r="N142" t="inlineStr">
         <is>
           <t>primary</t>
@@ -10196,7 +9724,6 @@
           <t>https://www.basketball.qc.ca/fr/page/reseau_basketball_quebec/sud-ouest.html</t>
         </is>
       </c>
-      <c r="P142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -10219,7 +9746,6 @@
           <t>Saint-Lin-Laurentides</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
           <t>514-207-1777</t>
@@ -10327,13 +9853,11 @@
           <t>Training academy; also runs the sport-études basketball program at École secondaire De Mortagne (Boucherville)</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
       <c r="L144" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M144" t="inlineStr"/>
       <c r="N144" t="inlineStr">
         <is>
           <t>primary</t>
@@ -10391,19 +9915,16 @@
           <t>http://www.mtgbasketball.com</t>
         </is>
       </c>
-      <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr">
         <is>
           <t>Youth basketball (Basketball Québec affiliate)</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
       <c r="L145" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M145" t="inlineStr"/>
       <c r="N145" t="inlineStr">
         <is>
           <t>primary</t>
@@ -10441,14 +9962,11 @@
           <t>Sainte-Thérèse</t>
         </is>
       </c>
-      <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
           <t>450-419-8786</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr"/>
-      <c r="H146" t="inlineStr"/>
       <c r="I146" t="inlineStr">
         <is>
           <t>Jacinthe Lussier</t>
@@ -10459,13 +9977,11 @@
           <t>sport-étudiant</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
       <c r="L146" t="inlineStr">
         <is>
           <t>school sport network</t>
         </is>
       </c>
-      <c r="M146" t="inlineStr"/>
       <c r="N146" t="inlineStr">
         <is>
           <t>primary</t>
@@ -10476,7 +9992,6 @@
           <t>Basketball Québec regional registry PDFs (mined 2026-07-18)</t>
         </is>
       </c>
-      <c r="P146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -10499,14 +10014,11 @@
           <t>Sept-Îles</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
           <t>418-968-3731</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr"/>
-      <c r="H147" t="inlineStr"/>
       <c r="I147" t="inlineStr">
         <is>
           <t>Cindy Hounsell</t>
@@ -10527,7 +10039,6 @@
           <t>fédération sport-étudiant (RSEQ)</t>
         </is>
       </c>
-      <c r="M147" t="inlineStr"/>
       <c r="N147" t="inlineStr">
         <is>
           <t>primary</t>
@@ -10538,7 +10049,6 @@
           <t>Basketball Québec regional registry PDFs (mined 2026-07-18)</t>
         </is>
       </c>
-      <c r="P147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -10561,7 +10071,6 @@
           <t>Shawinigan</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
           <t>819-852-5310</t>
@@ -10587,13 +10096,11 @@
           <t>Day camp 'Les Petits Sportifs'; mini-basketball; Basketball Profile program at École secondaire du Rocher (4-8 periods/week) with strength training, CrossFit, yoga, nutrition/mental-prep</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
       <c r="L148" t="inlineStr">
         <is>
           <t>community nonprofit (youth development through sport)</t>
         </is>
       </c>
-      <c r="M148" t="inlineStr"/>
       <c r="N148" t="inlineStr">
         <is>
           <t>primary</t>
@@ -10604,7 +10111,6 @@
           <t>https://www.espacelelab.ca/</t>
         </is>
       </c>
-      <c r="P148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -10627,7 +10133,6 @@
           <t>Shawinigan</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
           <t>819-852-5310</t>
@@ -10653,13 +10158,11 @@
           <t>Nonprofit: mini-basketball fall/winter sessions, year-round basketball skills camps, summer day camp, flag-football, secondary-school basketball profile program</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
       <c r="L149" t="inlineStr">
         <is>
           <t>community nonprofit (basketball-first, some multi-sport)</t>
         </is>
       </c>
-      <c r="M149" t="inlineStr"/>
       <c r="N149" t="inlineStr">
         <is>
           <t>verified</t>
@@ -10670,7 +10173,6 @@
           <t>http://espacelelab.ca</t>
         </is>
       </c>
-      <c r="P149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -10708,7 +10210,6 @@
           <t>olirobert17@outlook.com</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr">
         <is>
           <t>Olivier Robert — contact in Basketball Québec directory (role unspecified)</t>
@@ -10719,13 +10220,11 @@
           <t>Organizes the Tournoi Invitation des Montagnards (youth basketball tournament)</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
       <c r="L150" t="inlineStr">
         <is>
           <t>uncertain — appears school-affiliated (Val-Mauricie 'Montagnards') tournament/program organizer</t>
         </is>
       </c>
-      <c r="M150" t="inlineStr"/>
       <c r="N150" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -10803,7 +10302,6 @@
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M151" t="inlineStr"/>
       <c r="N151" t="inlineStr">
         <is>
           <t>verified</t>
@@ -10871,13 +10369,11 @@
           <t>Youth basketball academy: boys U15/U16/U17 and girls U16/U17 teams, training sessions, training camps and tournaments</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
       <c r="L152" t="inlineStr">
         <is>
           <t>college-affiliated youth academy</t>
         </is>
       </c>
-      <c r="M152" t="inlineStr"/>
       <c r="N152" t="inlineStr">
         <is>
           <t>reported</t>
@@ -10945,7 +10441,6 @@
           <t>Youth club teams U15/U16/U17 male, U16/U17 female ($600/season: 18 weekly practices, 3 tournaments + friendlies); summer camps grades 5-6 to collegial ($300-375)</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr">
         <is>
           <t>institution-run youth academy (cégep)</t>
@@ -10993,14 +10488,11 @@
           <t>Sherbrooke</t>
         </is>
       </c>
-      <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
           <t>819-993-7536</t>
         </is>
       </c>
-      <c r="G154" t="inlineStr"/>
-      <c r="H154" t="inlineStr"/>
       <c r="I154" t="inlineStr">
         <is>
           <t>Pier-Luc Chiasson-Ricard</t>
@@ -11011,13 +10503,11 @@
           <t>de petit basket à juvénile *féminin et masculin</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
       <c r="L154" t="inlineStr">
         <is>
           <t>club</t>
         </is>
       </c>
-      <c r="M154" t="inlineStr"/>
       <c r="N154" t="inlineStr">
         <is>
           <t>primary</t>
@@ -11028,7 +10518,6 @@
           <t>Basketball Québec regional registry PDFs (mined 2026-07-18)</t>
         </is>
       </c>
-      <c r="P154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -11081,7 +10570,6 @@
           <t>Mini-basket (grades 1-6, Saturday sessions incl. BQ affiliation); Équipes Estrie regional identification teams (Espoirs du Québec regional coordinator); wheelchair basketball. Recognized by City of Sherbrooke and Conseil sport loisir de l'Estrie</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr">
         <is>
           <t>community nonprofit</t>
@@ -11159,7 +10647,6 @@
           <t>Mini-Panthers intro (12 sessions); Panthers Development (26 sessions); competitive/select teams U15-U17 male and female</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
       <c r="L156" t="inlineStr">
         <is>
           <t>community nonprofit (select/rep program)</t>
@@ -11180,7 +10667,6 @@
           <t>https://pantherssherbrooke.com/</t>
         </is>
       </c>
-      <c r="P156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -11315,7 +10801,6 @@
           <t>Junior Gaiters (grades 1-2, 3-4, 5-6); Gaiters Select (high-school age); Gaiters Elite; individual coaching; August player development camp; bilingual coaching</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr">
         <is>
           <t>private academy (affiliated with Bishop's University Gaiters)</t>
@@ -11445,14 +10930,11 @@
           <t>Ste-Foy</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
         <is>
           <t>(418) 657-7678</t>
         </is>
       </c>
-      <c r="G160" t="inlineStr"/>
-      <c r="H160" t="inlineStr"/>
       <c r="I160" t="inlineStr">
         <is>
           <t>Daniel Allie</t>
@@ -11463,13 +10945,11 @@
           <t>Sport étudiant</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
       <c r="L160" t="inlineStr">
         <is>
           <t>School sport federation</t>
         </is>
       </c>
-      <c r="M160" t="inlineStr"/>
       <c r="N160" t="inlineStr">
         <is>
           <t>primary</t>
@@ -11480,7 +10960,6 @@
           <t>Basketball Québec regional registry PDFs (mined 2026-07-18)</t>
         </is>
       </c>
-      <c r="P160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -11503,7 +10982,6 @@
           <t>Terrebonne</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr">
         <is>
           <t>514-757-5300</t>
@@ -11514,7 +10992,6 @@
           <t>acad.femininetempetedelarctique@gmail.com</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr"/>
       <c r="I161" t="inlineStr">
         <is>
           <t>Nadine Devalis — Basketball Québec registry contact</t>
@@ -11525,13 +11002,11 @@
           <t>Girls basketball academy</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
       <c r="L161" t="inlineStr">
         <is>
           <t>private academy (girls-focused)</t>
         </is>
       </c>
-      <c r="M161" t="inlineStr"/>
       <c r="N161" t="inlineStr">
         <is>
           <t>primary</t>
@@ -11569,7 +11044,6 @@
           <t>Terrebonne</t>
         </is>
       </c>
-      <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
           <t>514-296-8449</t>
@@ -11580,7 +11054,6 @@
           <t>rombball.basket@gmail.com</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr"/>
       <c r="I162" t="inlineStr">
         <is>
           <t>Romain Brutus — Basketball Québec registry contact</t>
@@ -11591,13 +11064,11 @@
           <t>Youth basketball training (Basketball Québec affiliate)</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
       <c r="L162" t="inlineStr">
         <is>
           <t>private academy/training (assumed from naming; not confirmed)</t>
         </is>
       </c>
-      <c r="M162" t="inlineStr"/>
       <c r="N162" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -11635,7 +11106,6 @@
           <t>Terrebonne / Mascouche</t>
         </is>
       </c>
-      <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr">
         <is>
           <t>1-888-569-2268</t>
@@ -11661,7 +11131,6 @@
           <t>Rec 4-7, 12-13, 14-17; competitive 8-17 registered in regional and provincial leagues; elite program; 6-week day camps; free community sessions</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
       <c r="L163" t="inlineStr">
         <is>
           <t>community nonprofit</t>
@@ -11709,7 +11178,6 @@
           <t>Terrebonne / Rosemère</t>
         </is>
       </c>
-      <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
           <t>514-867-1205</t>
@@ -11760,7 +11228,6 @@
           <t>https://www.revolutionbasket.com/fr/index.html</t>
         </is>
       </c>
-      <c r="P164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -11788,7 +11255,6 @@
           <t>803 Route 112, Saint-Joseph-de-Coleraine, QC G0N 1B0</t>
         </is>
       </c>
-      <c r="F165" t="inlineStr"/>
       <c r="G165" t="inlineStr">
         <is>
           <t>info@atelier803.ca</t>
@@ -11819,7 +11285,6 @@
           <t>private academy (with nonprofit fundraising campaigns)</t>
         </is>
       </c>
-      <c r="M165" t="inlineStr"/>
       <c r="N165" t="inlineStr">
         <is>
           <t>verified</t>
@@ -11862,7 +11327,6 @@
           <t>803 Route 112, Saint-Joseph-de-Coleraine, QC G0N 1B0</t>
         </is>
       </c>
-      <c r="F166" t="inlineStr"/>
       <c r="G166" t="inlineStr">
         <is>
           <t>info@atelier803.ca</t>
@@ -11893,7 +11357,6 @@
           <t>private academy</t>
         </is>
       </c>
-      <c r="M166" t="inlineStr"/>
       <c r="N166" t="inlineStr">
         <is>
           <t>primary</t>
@@ -11931,7 +11394,6 @@
           <t>Trois-Pistoles</t>
         </is>
       </c>
-      <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr">
         <is>
           <t>418-863-3167</t>
@@ -11942,20 +11404,16 @@
           <t>basketdesbasques@gmail.com</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr"/>
       <c r="I167" t="inlineStr">
         <is>
           <t>Samuel Dionne — contact in Basketball Québec directory (role unspecified)</t>
         </is>
       </c>
-      <c r="J167" t="inlineStr"/>
-      <c r="K167" t="inlineStr"/>
       <c r="L167" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M167" t="inlineStr"/>
       <c r="N167" t="inlineStr">
         <is>
           <t>primary</t>
@@ -11993,10 +11451,6 @@
           <t>Trois-Rivières</t>
         </is>
       </c>
-      <c r="E168" t="inlineStr"/>
-      <c r="F168" t="inlineStr"/>
-      <c r="G168" t="inlineStr"/>
-      <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr">
         <is>
           <t>Patrice Deltell</t>
@@ -12007,13 +11461,11 @@
           <t>de 12 à 17 ans sport-études</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
       <c r="L168" t="inlineStr">
         <is>
           <t>Basketball Club / Sport-Études Academy</t>
         </is>
       </c>
-      <c r="M168" t="inlineStr"/>
       <c r="N168" t="inlineStr">
         <is>
           <t>primary</t>
@@ -12024,7 +11476,6 @@
           <t>Basketball Québec regional registry PDFs (mined 2026-07-18)</t>
         </is>
       </c>
-      <c r="P168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -12077,13 +11528,11 @@
           <t>Promotes/develops youth basketball ages 8-12 (novice &amp; mini, boys and girls per PSO PDF)</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
       <c r="L169" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M169" t="inlineStr"/>
       <c r="N169" t="inlineStr">
         <is>
           <t>verified</t>
@@ -12121,27 +11570,21 @@
           <t>Trois-Rivières</t>
         </is>
       </c>
-      <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr">
         <is>
           <t>(819) 693-5805 poste 6543</t>
         </is>
       </c>
-      <c r="G170" t="inlineStr"/>
-      <c r="H170" t="inlineStr"/>
       <c r="I170" t="inlineStr">
         <is>
           <t>Michelline Guillemette</t>
         </is>
       </c>
-      <c r="J170" t="inlineStr"/>
-      <c r="K170" t="inlineStr"/>
       <c r="L170" t="inlineStr">
         <is>
           <t>Student Sport Network</t>
         </is>
       </c>
-      <c r="M170" t="inlineStr"/>
       <c r="N170" t="inlineStr">
         <is>
           <t>primary</t>
@@ -12152,7 +11595,6 @@
           <t>Basketball Québec regional registry PDFs (mined 2026-07-18)</t>
         </is>
       </c>
-      <c r="P170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -12205,7 +11647,6 @@
           <t>Summer basketball camps since 2012 for primary and secondary athletes across Mauricie (35 hrs over 2 weeks, held in Académie les Estacades gyms); psychomotricity/basketball program for young children</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
       <c r="L171" t="inlineStr">
         <is>
           <t>private camp organization</t>
@@ -12253,7 +11694,6 @@
           <t>Varennes</t>
         </is>
       </c>
-      <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr">
         <is>
           <t>514-923-6147</t>
@@ -12264,7 +11704,6 @@
           <t>basketballvarennes@gmail.com</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr">
         <is>
           <t>Alexandre Rivet — contact/lead</t>
@@ -12275,13 +11714,11 @@
           <t>Youth basketball (Basketball Québec affiliate)</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
       <c r="L172" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M172" t="inlineStr"/>
       <c r="N172" t="inlineStr">
         <is>
           <t>primary</t>
@@ -12292,7 +11729,6 @@
           <t>https://www.basketball.qc.ca/fr/page/reseau_basketball_quebec/rive-sud.html</t>
         </is>
       </c>
-      <c r="P172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -12315,14 +11751,11 @@
           <t>Vaudreuil-Soulanges</t>
         </is>
       </c>
-      <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr">
         <is>
           <t>450-374-8044</t>
         </is>
       </c>
-      <c r="G173" t="inlineStr"/>
-      <c r="H173" t="inlineStr"/>
       <c r="I173" t="inlineStr">
         <is>
           <t>Cynthia Frégeau — contact (PSO registry)</t>
@@ -12333,13 +11766,11 @@
           <t>Development program, individual skills, petit basket to juvénile, boys and girls</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
       <c r="L173" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M173" t="inlineStr"/>
       <c r="N173" t="inlineStr">
         <is>
           <t>primary</t>
@@ -12377,14 +11808,11 @@
           <t>Victoriaville</t>
         </is>
       </c>
-      <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr">
         <is>
           <t>819-460-8080</t>
         </is>
       </c>
-      <c r="G174" t="inlineStr"/>
-      <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr">
         <is>
           <t>Andrée Brière</t>
@@ -12395,13 +11823,11 @@
           <t>de novice à juvénile *fém&amp;masc</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
       <c r="L174" t="inlineStr">
         <is>
           <t>club</t>
         </is>
       </c>
-      <c r="M174" t="inlineStr"/>
       <c r="N174" t="inlineStr">
         <is>
           <t>primary</t>
@@ -12412,7 +11838,6 @@
           <t>Basketball Québec regional registry PDFs (mined 2026-07-18)</t>
         </is>
       </c>
-      <c r="P174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -12475,7 +11900,6 @@
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M175" t="inlineStr"/>
       <c r="N175" t="inlineStr">
         <is>
           <t>verified</t>
@@ -12513,7 +11937,6 @@
           <t>Warwick</t>
         </is>
       </c>
-      <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr">
         <is>
           <t>819-806-9737</t>
@@ -12539,13 +11962,11 @@
           <t>Mini-basket program run through Ville de Warwick fall programming</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
       <c r="L176" t="inlineStr">
         <is>
           <t>community/municipal program</t>
         </is>
       </c>
-      <c r="M176" t="inlineStr"/>
       <c r="N176" t="inlineStr">
         <is>
           <t>primary</t>
@@ -12578,15 +11999,11 @@
           <t>Saguenay/Lac St-Jean</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr"/>
-      <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr">
         <is>
           <t>(418) 543-3532 #1213</t>
         </is>
       </c>
-      <c r="G177" t="inlineStr"/>
-      <c r="H177" t="inlineStr"/>
       <c r="I177" t="inlineStr">
         <is>
           <t>Eric Benoît</t>
@@ -12597,13 +12014,11 @@
           <t>Sport-étudiant</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
       <c r="L177" t="inlineStr">
         <is>
           <t>Sport-étudiant network (school sport)</t>
         </is>
       </c>
-      <c r="M177" t="inlineStr"/>
       <c r="N177" t="inlineStr">
         <is>
           <t>primary</t>
@@ -12614,7 +12029,6 @@
           <t>Basketball Québec regional registry PDFs (mined 2026-07-18)</t>
         </is>
       </c>
-      <c r="P177" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:P177"/>
@@ -13058,7 +12472,6 @@
           <t>3 sessions of 8 weeks each: fall, winter, spring; Dragons fall-winter season late August–late March</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>info@basketballgatineau.com</t>
@@ -13307,7 +12720,6 @@
           <t>Amilia for online registration</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>primary</t>
@@ -13350,14 +12762,11 @@
           <t>Laval</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Shopify storefront on own domain for league/program registration (millerbasketballacademy.ca/products/...)</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>reported</t>
@@ -13400,13 +12809,11 @@
           <t>Quebec City (multiple school and municipal gyms)</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>School-year sessions (weekend courses + leagues); winter league documented</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>embq@embq.qc.ca, (581) 741-6658</t>
@@ -15538,14 +14945,11 @@
           <t>Alma</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>Simon Leblanc, Cyrille Poitevineau-Millin, Samuel Guay — co-founders</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -15558,13 +14962,11 @@
           <t>Baie-Comeau</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>abmbc01@gmail.com</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>https://www.facebook.com/profile.php?id=100076065697206</t>
@@ -15587,9 +14989,6 @@
           <t>(418) 589-5774</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -15809,7 +15208,6 @@
           <t>Jacob Petricich — contact/lead</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -15837,7 +15235,6 @@
           <t>Christopher Pierre — contact/lead</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -15919,13 +15316,11 @@
           <t>(819) 864-0792</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>Olivier Audet</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -15943,9 +15338,6 @@
           <t>(418) 745-3968</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -16059,7 +15451,6 @@
           <t>514-898-2637</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>Jonathan Sergue — contact/lead (PSO registry)</t>
@@ -16215,9 +15606,6 @@
           <t>(819) 478-1483</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -16309,7 +15697,6 @@
           <t>David Chamoun — contact per Basketball Québec regional registry</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -16369,7 +15756,6 @@
           <t>Joel Belleau — Basketball Québec registry contact</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -16446,14 +15832,11 @@
           <t>Gatineau</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
           <t>Jean Duchesne</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -16503,13 +15886,11 @@
           <t>(819) 643-6663</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
           <t>Hélène Boucher</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -16537,7 +15918,6 @@
           <t>Joel Belleau — contact per Basketball Québec regional registry</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -16592,7 +15972,6 @@
           <t>info@gmsgranby.org</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>https://granbymultisports.ca/activite/mini-basket/</t>
@@ -16647,13 +16026,11 @@
           <t>418-376-4281</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
           <t>Jean Ménard</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -16671,9 +16048,6 @@
           <t>1-866-588-4443</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -16701,7 +16075,6 @@
           <t>Mélanie Gauthier — contact (same person as EMBQ administration)</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -16729,7 +16102,6 @@
           <t>Laurent Fournier — contact in Basketball Québec directory (role unspecified)</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -16757,7 +16129,6 @@
           <t>Laurent Fournier (PSO-listed contact)</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -16775,13 +16146,11 @@
           <t>(514) 970-2232</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
           <t>David Osmann</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -16799,13 +16168,11 @@
           <t>(514) 970-2232</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
           <t>David Osmann — contact (PSO registry)</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -16855,13 +16222,11 @@
           <t>514-464-5203</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>Eric Denis</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -16943,13 +16308,11 @@
           <t>(450) 664-1917</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
           <t>Martin Savoie</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -16962,14 +16325,11 @@
           <t>Limoilou</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
           <t>Martin Thibault</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -17051,7 +16411,6 @@
           <t>(418) 930-7525</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
           <t>Pascal Dubé — owner/head coach (20 yrs coaching, B.Sc. sports intervention Université Laval)</t>
@@ -17212,7 +16571,6 @@
           <t>info@alphacommunity.ca</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>https://www.alphacommunity.ca/</t>
@@ -17277,7 +16635,6 @@
           <t>Mamadou Fofana — contact</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -17337,7 +16694,6 @@
           <t>Pany Phetxayakhoth — contact</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -17365,7 +16721,6 @@
           <t>Leon Arabian — contact</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -17681,7 +17036,6 @@
           <t>Edgardo Tupaz — contact/organizer</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -17763,13 +17117,11 @@
           <t>514-788-3938</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
           <t>Sébastien Babeux — contact (PSO registry)</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -17829,7 +17181,6 @@
           <t>Janet Lawrence — contact (Basketball Québec); Avrom Coodin — contact (PSO PDF)</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -18103,13 +17454,11 @@
           <t>514-207-1814</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
           <t>Yasser Mohammad — contact (PSO registry)</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -18191,13 +17540,11 @@
           <t>514-931-8731 #5032</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
           <t>Joel Tyrrell — contact (PSO registry)</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -18215,9 +17562,6 @@
           <t>514-885-8176</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -18235,7 +17579,6 @@
           <t>514-616-5819</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
           <t>Joel Casseus, Ricky Volcy, Ricardo Telamon — co-founders (2017)</t>
@@ -18268,7 +17611,6 @@
           <t>info@crer.me</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
           <t>https://crer.me/club-sportif/basketball-montreal-est/</t>
@@ -18291,13 +17633,11 @@
           <t>514-774-1663</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
           <t>Michel Bento</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -18416,7 +17756,6 @@
           <t>info@byfarsports.com</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
           <t>https://byfarsports.com/</t>
@@ -18449,7 +17788,6 @@
           <t>Aurélien Puech — contact in Basketball Québec directory (role unspecified)</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -18462,7 +17800,6 @@
           <t>Québec City</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
           <t>edembasketball@gmail.com</t>
@@ -18473,7 +17810,6 @@
           <t>Sophia Laababsi — contact in PSO registry (role unspecified)</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -18523,7 +17859,6 @@
           <t>418-953-7504</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
           <t>Modibo Diarra — founder/head trainer (6'10" former NBL Canada player, Saint John Mill Rats)</t>
@@ -18578,7 +17913,6 @@
           <t>Québec City</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr">
         <is>
           <t>onemorebasketball1@gmail.com</t>
@@ -18621,7 +17955,6 @@
           <t>Guillaume L'Ecuyer — contact in Basketball Québec directory (role unspecified)</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -18634,7 +17967,6 @@
           <t>Québec City</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
           <t>ecolebbemonkam1@gmail.com</t>
@@ -18677,7 +18009,6 @@
           <t>Mélanie Gauthier (PSO-listed contact; also EMBQ administration)</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -18727,13 +18058,11 @@
           <t>418-805-6205</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
           <t>Marc-André Dugas (PSO-listed contact; club initials match his name)</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -18815,13 +18144,11 @@
           <t>(450) 463-4055 Poste 102</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
           <t>Sylvie Cornellier</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -18871,13 +18198,11 @@
           <t>418-723-1880 #2539</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
           <t>Marc Boudreau</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -18905,7 +18230,6 @@
           <t>Keven Morneau — contact in Basketball Québec directory (school board email; role unspecified)</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -18923,9 +18247,6 @@
           <t>(819) 864-0864</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
-      <c r="E118" t="inlineStr"/>
-      <c r="F118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -18943,13 +18264,11 @@
           <t>514-746-3478</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
           <t>David Roy — contact/lead (PSO registry)</t>
         </is>
       </c>
-      <c r="F119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -18967,13 +18286,11 @@
           <t>514-972-6765</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
           <t>Pascal Fleury</t>
         </is>
       </c>
-      <c r="F120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -19087,7 +18404,6 @@
           <t>418-542-7536 ext. 117</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr">
         <is>
           <t>Sophie Bouchard, General Director</t>
@@ -19221,7 +18537,6 @@
           <t>Maïka Baril — contact in Basketball Québec directory (role unspecified)</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -19345,7 +18660,6 @@
           <t>Adrian Enache — contact/lead</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -19427,9 +18741,6 @@
           <t>(450) 773-9802</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
-      <c r="E135" t="inlineStr"/>
-      <c r="F135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -19447,13 +18758,11 @@
           <t>514-885-4347</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
           <t>Patrick Kervin</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -19641,7 +18950,6 @@
           <t>Sophie Plante — contact/lead</t>
         </is>
       </c>
-      <c r="F142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -19728,7 +19036,6 @@
           <t>info@mtgbasketball.com</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
           <t>http://www.mtgbasketball.com</t>
@@ -19751,13 +19058,11 @@
           <t>450-419-8786</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr">
         <is>
           <t>Jacinthe Lussier</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -19775,13 +19080,11 @@
           <t>418-968-3731</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr">
         <is>
           <t>Cindy Hounsell</t>
         </is>
       </c>
-      <c r="F147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -19873,7 +19176,6 @@
           <t>Olivier Robert — contact in Basketball Québec directory (role unspecified)</t>
         </is>
       </c>
-      <c r="F150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -19987,13 +19289,11 @@
           <t>819-993-7536</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr">
         <is>
           <t>Pier-Luc Chiasson-Ricard</t>
         </is>
       </c>
-      <c r="F154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -20171,13 +19471,11 @@
           <t>(418) 657-7678</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
           <t>Daniel Allie</t>
         </is>
       </c>
-      <c r="F160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -20205,7 +19503,6 @@
           <t>Nadine Devalis — Basketball Québec registry contact</t>
         </is>
       </c>
-      <c r="F161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -20233,7 +19530,6 @@
           <t>Romain Brutus — Basketball Québec registry contact</t>
         </is>
       </c>
-      <c r="F162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -20310,7 +19606,6 @@
           <t>Thetford Mines (Saint-Joseph-de-Coleraine)</t>
         </is>
       </c>
-      <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr">
         <is>
           <t>info@atelier803.ca</t>
@@ -20338,7 +19633,6 @@
           <t>Thetford Mines (Saint-Joseph-de-Coleraine)</t>
         </is>
       </c>
-      <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr">
         <is>
           <t>info@atelier803.ca</t>
@@ -20381,7 +19675,6 @@
           <t>Samuel Dionne — contact in Basketball Québec directory (role unspecified)</t>
         </is>
       </c>
-      <c r="F167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -20394,14 +19687,11 @@
           <t>Trois-Rivières</t>
         </is>
       </c>
-      <c r="C168" t="inlineStr"/>
-      <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr">
         <is>
           <t>Patrice Deltell</t>
         </is>
       </c>
-      <c r="F168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -20451,13 +19741,11 @@
           <t>(819) 693-5805 poste 6543</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr">
         <is>
           <t>Michelline Guillemette</t>
         </is>
       </c>
-      <c r="F170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -20517,7 +19805,6 @@
           <t>Alexandre Rivet — contact/lead</t>
         </is>
       </c>
-      <c r="F172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -20535,13 +19822,11 @@
           <t>450-374-8044</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr">
         <is>
           <t>Cynthia Frégeau — contact (PSO registry)</t>
         </is>
       </c>
-      <c r="F173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -20559,13 +19844,11 @@
           <t>819-460-8080</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr">
         <is>
           <t>Andrée Brière</t>
         </is>
       </c>
-      <c r="F174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -20637,22 +19920,386 @@
           <t>RSEQ</t>
         </is>
       </c>
-      <c r="B177" t="inlineStr"/>
       <c r="C177" t="inlineStr">
         <is>
           <t>(418) 543-3532 #1213</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr">
         <is>
           <t>Eric Benoît</t>
         </is>
       </c>
-      <c r="F177" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F177"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Club</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Teams counted (directional)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Breakdown (league=teams)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Tornades</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>13</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Montreal Basketball League (MBL)=13</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Lasalle Leaders</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>12</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Montreal Basketball League (MBL)=12</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Brookwood</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>11</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Montreal Basketball League (MBL)=11</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>DC Blues</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>11</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Montreal Basketball League (MBL)=11</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Pagé Concordia</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>10</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Montreal Basketball League (MBL)=10</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Laval Nobel</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>10</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Montreal Basketball League (MBL)=10</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Monarques</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>9</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Montreal Basketball League (MBL)=9</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>West Island Lakers</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>9</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Montreal Basketball League (MBL)=9</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>St Jean Riverains</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Montreal Basketball League (MBL)=9</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Club Basket de l'Ouest (Cavaliers)</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>7</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Montreal Basketball League (MBL)=7</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>DBC Hawks/Bobcats</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>7</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Montreal Basketball League (MBL)=7</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Chateauguay Ravens</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>7</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Montreal Basketball League (MBL)=7</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Parc Ex Knights</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Montreal Basketball League (MBL)=6</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Sun Youth Hornets</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>6</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Montreal Basketball League (MBL)=6</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>YMHA Wolves</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>6</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Montreal Basketball League (MBL)=6</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>St-Laurent Lynx</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Montreal Basketball League (MBL)=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Uptown Huskies</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>4</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Montreal Basketball League (MBL)=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>St-Hubert Lynx</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Montreal Basketball League (MBL)=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Cote St-Luc Warriors</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>3</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Montreal Basketball League (MBL)=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Revolution</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Montreal Basketball League (MBL)=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>DBC St-Constant</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Montreal Basketball League (MBL)=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>DOD-Basketball</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Montreal Basketball League (MBL)=1</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C23"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/research/provinces/SportsHub-Quebec.xlsx
+++ b/docs/research/provinces/SportsHub-Quebec.xlsx
@@ -14,7 +14,7 @@
     <sheet name="Club Sizes" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Clubs'!$A$1:$P$177</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Clubs'!$A$1:$Q$177</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Leagues'!$A$1:$L$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Club-League Map'!$A$1:$E$81</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Contacts'!$A$1:$F$177</definedName>
@@ -65,11 +65,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P177"/>
+  <dimension ref="A1:Q177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -454,6 +455,7 @@
     <col width="11" customWidth="1" min="14" max="14"/>
     <col width="30" customWidth="1" min="15" max="15"/>
     <col width="30" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -537,6 +539,11 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>Teams Counted</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5419,6 +5426,9 @@
           <t>https://leadersbasketball.com/pages/novice</t>
         </is>
       </c>
+      <c r="Q77" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5754,6 +5764,9 @@
           <t>Basketball arm of Loisirs du Parc community centre</t>
         </is>
       </c>
+      <c r="Q82" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5903,6 +5916,9 @@
           <t>Large multi-service community nonprofit</t>
         </is>
       </c>
+      <c r="Q84" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -6114,6 +6130,9 @@
           <t>PSO Montréal PDF lists as 'DOD Basketball/EMBC Avatars'</t>
         </is>
       </c>
+      <c r="Q87" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -6831,6 +6850,9 @@
           <t>TeamSnap = direct competitive-platform intel</t>
         </is>
       </c>
+      <c r="Q98" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -12031,7 +12053,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P177"/>
+  <autoFilter ref="A1:Q177"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
